--- a/04 Working Files/metafields.xlsx
+++ b/04 Working Files/metafields.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dschriver\Desktop\Claude CoWork\Projects\Shopify Catalog Update\04 Working Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E81B48E4-88FD-41C1-BB5B-BAD039653CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C257B0-4525-4BA6-97CE-BF13A98FB243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5760" yWindow="375" windowWidth="17520" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -272,10 +272,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -544,8 +540,8 @@
   <dimension ref="A1:C106"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" customWidth="1"/>
-    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="27.5703125" customWidth="1"/>
     <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
